--- a/result/C201_Test.xlsx
+++ b/result/C201_Test.xlsx
@@ -458,7 +458,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E4" s="3">
-        <v>109.69</v>
+        <v>152.17</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,7 +475,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E5" s="3">
-        <v>109.69</v>
+        <v>152.17</v>
       </c>
     </row>
   </sheetData>
